--- a/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>CRWE</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,11 +846,11 @@
         <v>0</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1293,8 +1313,8 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1302,11 +1322,11 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1324,16 +1344,16 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
@@ -1341,20 +1361,20 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1436,8 +1459,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>4</v>
@@ -1445,11 +1468,11 @@
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>4</v>
@@ -1457,8 +1480,8 @@
       <c r="AC15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1523,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1509,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3">
         <v>100</v>
@@ -1539,25 +1566,25 @@
         <v>100</v>
       </c>
       <c r="P17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W17" s="3">
         <v>100</v>
@@ -1566,31 +1593,34 @@
         <v>100</v>
       </c>
       <c r="Y17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z17" s="3">
         <v>0</v>
       </c>
       <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
         <v>100</v>
       </c>
-      <c r="AB17" s="3">
-        <v>0</v>
-      </c>
       <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3">
         <v>100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
-        <v>0</v>
-      </c>
       <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1601,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
         <v>-100</v>
@@ -1631,25 +1661,25 @@
         <v>-100</v>
       </c>
       <c r="P18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3">
         <v>-100</v>
@@ -1658,31 +1688,34 @@
         <v>-100</v>
       </c>
       <c r="Y18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z18" s="3">
         <v>0</v>
       </c>
       <c r="AA18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
-        <v>0</v>
-      </c>
       <c r="AF18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1748,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1733,17 +1767,17 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1769,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1807,8 +1841,11 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1819,20 +1856,20 @@
         <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
         <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
-        <v>-100</v>
-      </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
@@ -1840,23 +1877,23 @@
         <v>-100</v>
       </c>
       <c r="M21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
-        <v>-100</v>
-      </c>
       <c r="O21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
         <v>0</v>
       </c>
@@ -1867,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="V21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
         <v>-100</v>
       </c>
       <c r="X21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y21" s="3">
         <v>0</v>
@@ -1881,8 +1918,8 @@
       <c r="Z21" s="3">
         <v>0</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
+      <c r="AA21" s="3">
+        <v>0</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
@@ -1890,17 +1927,20 @@
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-300</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
       <c r="AF21" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1934,11 +1974,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1991,8 +2031,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2003,20 +2046,20 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
         <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
-        <v>-100</v>
-      </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
@@ -2024,31 +2067,31 @@
         <v>-100</v>
       </c>
       <c r="M23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-200</v>
       </c>
-      <c r="N23" s="3">
-        <v>-100</v>
-      </c>
       <c r="O23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
         <v>-100</v>
@@ -2060,31 +2103,34 @@
         <v>-100</v>
       </c>
       <c r="Y23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z23" s="3">
         <v>0</v>
       </c>
       <c r="AA23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2316,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2279,20 +2331,20 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
         <v>-100</v>
       </c>
       <c r="H26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
-        <v>-100</v>
-      </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
@@ -2300,31 +2352,31 @@
         <v>-100</v>
       </c>
       <c r="M26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
-        <v>-100</v>
-      </c>
       <c r="O26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
         <v>-100</v>
@@ -2336,31 +2388,34 @@
         <v>-100</v>
       </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z26" s="3">
         <v>0</v>
       </c>
       <c r="AA26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2371,20 +2426,20 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
         <v>-100</v>
       </c>
       <c r="H27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
-        <v>-100</v>
-      </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
@@ -2392,31 +2447,31 @@
         <v>-100</v>
       </c>
       <c r="M27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
-        <v>-100</v>
-      </c>
       <c r="O27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>-100</v>
@@ -2428,31 +2483,34 @@
         <v>-100</v>
       </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z27" s="3">
         <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2886,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2837,16 +2907,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2873,11 +2943,11 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2911,8 +2981,11 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2923,20 +2996,20 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
         <v>-100</v>
       </c>
       <c r="H33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
-        <v>-100</v>
-      </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
@@ -2944,31 +3017,31 @@
         <v>-100</v>
       </c>
       <c r="M33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
-        <v>-100</v>
-      </c>
       <c r="O33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
         <v>-100</v>
@@ -2980,31 +3053,34 @@
         <v>-100</v>
       </c>
       <c r="Y33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z33" s="3">
         <v>0</v>
       </c>
       <c r="AA33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3171,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3107,20 +3186,20 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
         <v>-100</v>
       </c>
       <c r="H35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
-        <v>-100</v>
-      </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
@@ -3128,31 +3207,31 @@
         <v>-100</v>
       </c>
       <c r="M35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
-        <v>-100</v>
-      </c>
       <c r="O35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>-100</v>
@@ -3164,128 +3243,134 @@
         <v>-100</v>
       </c>
       <c r="Y35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z35" s="3">
         <v>0</v>
       </c>
       <c r="AA35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3438,9 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3442,10 +3529,13 @@
         <v>0</v>
       </c>
       <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3455,8 +3545,8 @@
       <c r="E42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -3465,28 +3555,28 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>100</v>
-      </c>
-      <c r="N42" s="3">
-        <v>200</v>
       </c>
       <c r="O42" s="3">
         <v>200</v>
       </c>
       <c r="P42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3536,8 +3626,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3761,8 +3860,8 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
@@ -3779,8 +3878,8 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3833,28 +3935,28 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>100</v>
-      </c>
-      <c r="N46" s="3">
-        <v>200</v>
       </c>
       <c r="O46" s="3">
         <v>200</v>
       </c>
       <c r="P46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
@@ -3902,10 +4004,13 @@
         <v>0</v>
       </c>
       <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4053,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <v>100</v>
@@ -4070,8 +4178,8 @@
       <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
+      <c r="AA48" s="3">
+        <v>100</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,8 +4671,11 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4569,16 +4695,16 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
         <v>300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>100</v>
-      </c>
-      <c r="L54" s="3">
-        <v>200</v>
       </c>
       <c r="M54" s="3">
         <v>200</v>
@@ -4590,7 +4716,7 @@
         <v>200</v>
       </c>
       <c r="P54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="3">
         <v>0</v>
@@ -4605,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V54" s="3">
         <v>100</v>
@@ -4623,7 +4749,7 @@
         <v>100</v>
       </c>
       <c r="AA54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB54" s="3">
         <v>0</v>
@@ -4638,10 +4764,13 @@
         <v>0</v>
       </c>
       <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4723,40 +4854,40 @@
         <v>1400</v>
       </c>
       <c r="G57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>300</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
@@ -4780,7 +4911,7 @@
         <v>300</v>
       </c>
       <c r="Z57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA57" s="3">
         <v>200</v>
@@ -4800,8 +4931,11 @@
       <c r="AF57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4812,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -4821,14 +4955,14 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4842,13 +4976,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4892,28 +5026,31 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -4933,14 +5070,14 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -4949,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
@@ -4957,14 +5094,14 @@
       <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
+      <c r="X59" s="3">
+        <v>100</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4984,13 +5121,16 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E60" s="3">
         <v>1400</v>
@@ -4999,37 +5139,37 @@
         <v>1400</v>
       </c>
       <c r="G60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1300</v>
       </c>
       <c r="J60" s="3">
         <v>1300</v>
       </c>
       <c r="K60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
-      </c>
-      <c r="O60" s="3">
-        <v>500</v>
       </c>
       <c r="P60" s="3">
         <v>500</v>
       </c>
       <c r="Q60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
@@ -5041,13 +5181,13 @@
         <v>300</v>
       </c>
       <c r="U60" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V60" s="3">
         <v>400</v>
       </c>
       <c r="W60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X60" s="3">
         <v>300</v>
@@ -5059,7 +5199,7 @@
         <v>300</v>
       </c>
       <c r="AA60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB60" s="3">
         <v>200</v>
@@ -5076,8 +5216,11 @@
       <c r="AF60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,13 +5691,16 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E66" s="3">
         <v>1400</v>
@@ -5551,49 +5709,49 @@
         <v>1400</v>
       </c>
       <c r="G66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1300</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L66" s="3">
         <v>900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
-      </c>
-      <c r="N66" s="3">
-        <v>600</v>
       </c>
       <c r="O66" s="3">
         <v>600</v>
       </c>
       <c r="P66" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q66" s="3">
         <v>500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>300</v>
       </c>
       <c r="R66" s="3">
         <v>300</v>
       </c>
       <c r="S66" s="3">
+        <v>300</v>
+      </c>
+      <c r="T66" s="3">
         <v>400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>400</v>
       </c>
       <c r="V66" s="3">
         <v>400</v>
@@ -5602,7 +5760,7 @@
         <v>400</v>
       </c>
       <c r="X66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y66" s="3">
         <v>300</v>
@@ -5611,7 +5769,7 @@
         <v>300</v>
       </c>
       <c r="AA66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB66" s="3">
         <v>200</v>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6201,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6045,85 +6219,88 @@
         <v>-14200</v>
       </c>
       <c r="G72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-14100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12300</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-11800</v>
       </c>
       <c r="S72" s="3">
         <v>-11800</v>
       </c>
       <c r="T72" s="3">
-        <v>-11700</v>
+        <v>-11800</v>
       </c>
       <c r="U72" s="3">
         <v>-11700</v>
       </c>
       <c r="V72" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="W72" s="3">
         <v>-11600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11400</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-11300</v>
       </c>
       <c r="Z72" s="3">
         <v>-11300</v>
       </c>
       <c r="AA72" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="AB72" s="3">
         <v>-11200</v>
       </c>
       <c r="AC72" s="3">
-        <v>-11100</v>
+        <v>-11200</v>
       </c>
       <c r="AD72" s="3">
         <v>-11100</v>
       </c>
       <c r="AE72" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,8 +6581,11 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6413,37 +6599,37 @@
         <v>-1400</v>
       </c>
       <c r="G76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H76" s="3">
         <v>-1300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-600</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-400</v>
       </c>
       <c r="O76" s="3">
         <v>-400</v>
       </c>
       <c r="P76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-300</v>
       </c>
       <c r="R76" s="3">
         <v>-300</v>
@@ -6467,7 +6653,7 @@
         <v>-300</v>
       </c>
       <c r="Y76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z76" s="3">
         <v>-200</v>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6771,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6691,20 +6886,20 @@
         <v>0</v>
       </c>
       <c r="F81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
         <v>-100</v>
       </c>
       <c r="H81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
-        <v>-100</v>
-      </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
@@ -6712,31 +6907,31 @@
         <v>-100</v>
       </c>
       <c r="M81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
-        <v>-100</v>
-      </c>
       <c r="O81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
         <v>-100</v>
@@ -6748,31 +6943,34 @@
         <v>-100</v>
       </c>
       <c r="Y81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z81" s="3">
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6879,8 +7078,8 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
@@ -6888,8 +7087,8 @@
       <c r="AC83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7571,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7986,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7783,22 +8013,22 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
@@ -7806,17 +8036,17 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8277,11 +8523,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -8292,11 +8538,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -8313,11 +8559,11 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8686,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>CRWE</t>
   </si>
@@ -656,144 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -849,14 +856,14 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
@@ -887,8 +894,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +995,14 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,13 +1335,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1316,23 +1355,23 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1347,40 +1386,40 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1397,8 +1436,14 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1462,38 +1507,44 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,25 +1575,27 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
       <c r="G17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
         <v>100</v>
@@ -1569,40 +1622,40 @@
         <v>100</v>
       </c>
       <c r="Q17" s="3">
+        <v>100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>100</v>
+      </c>
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3">
         <v>100</v>
       </c>
       <c r="Z17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
@@ -1611,16 +1664,22 @@
         <v>100</v>
       </c>
       <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,16 +1687,16 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>-100</v>
@@ -1664,40 +1723,40 @@
         <v>-100</v>
       </c>
       <c r="Q18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-100</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-100</v>
-      </c>
       <c r="X18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
         <v>-100</v>
       </c>
       <c r="Z18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="3">
         <v>0</v>
@@ -1706,16 +1765,22 @@
         <v>-100</v>
       </c>
       <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1814,10 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,20 +1837,20 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1806,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1844,8 +1911,14 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1853,34 +1926,34 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-100</v>
-      </c>
       <c r="M21" s="3">
         <v>-100</v>
       </c>
       <c r="N21" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O21" s="3">
         <v>-100</v>
@@ -1889,17 +1962,17 @@
         <v>-200</v>
       </c>
       <c r="Q21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
         <v>0</v>
       </c>
@@ -1907,40 +1980,46 @@
         <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA21" s="3">
         <v>0</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
+      <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>0</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-300</v>
       </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1977,14 +2056,14 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2034,43 +2113,49 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>0</v>
+      <c r="D23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-100</v>
-      </c>
       <c r="M23" s="3">
         <v>-100</v>
       </c>
       <c r="N23" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O23" s="3">
         <v>-100</v>
@@ -2079,17 +2164,17 @@
         <v>-200</v>
       </c>
       <c r="Q23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-100</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
@@ -2097,7 +2182,7 @@
         <v>-100</v>
       </c>
       <c r="W23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>-100</v>
@@ -2106,13 +2191,13 @@
         <v>-100</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="3">
         <v>0</v>
@@ -2121,16 +2206,22 @@
         <v>-100</v>
       </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,43 +2416,49 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>0</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-100</v>
-      </c>
       <c r="M26" s="3">
         <v>-100</v>
       </c>
       <c r="N26" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O26" s="3">
         <v>-100</v>
@@ -2364,17 +2467,17 @@
         <v>-200</v>
       </c>
       <c r="Q26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-100</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
@@ -2382,7 +2485,7 @@
         <v>-100</v>
       </c>
       <c r="W26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>-100</v>
@@ -2391,13 +2494,13 @@
         <v>-100</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="3">
         <v>0</v>
@@ -2406,51 +2509,57 @@
         <v>-100</v>
       </c>
       <c r="AE26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>0</v>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-100</v>
-      </c>
       <c r="M27" s="3">
         <v>-100</v>
       </c>
       <c r="N27" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O27" s="3">
         <v>-100</v>
@@ -2459,17 +2568,17 @@
         <v>-200</v>
       </c>
       <c r="Q27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-100</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
@@ -2477,7 +2586,7 @@
         <v>-100</v>
       </c>
       <c r="W27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>-100</v>
@@ -2486,13 +2595,13 @@
         <v>-100</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="3">
         <v>0</v>
@@ -2501,16 +2610,22 @@
         <v>-100</v>
       </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +3022,14 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2910,19 +3049,19 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2946,14 +3085,14 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2984,43 +3123,49 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>0</v>
+      <c r="D33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-100</v>
-      </c>
       <c r="M33" s="3">
         <v>-100</v>
       </c>
       <c r="N33" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O33" s="3">
         <v>-100</v>
@@ -3029,17 +3174,17 @@
         <v>-200</v>
       </c>
       <c r="Q33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-100</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
@@ -3047,7 +3192,7 @@
         <v>-100</v>
       </c>
       <c r="W33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X33" s="3">
         <v>-100</v>
@@ -3056,13 +3201,13 @@
         <v>-100</v>
       </c>
       <c r="Z33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="3">
         <v>0</v>
@@ -3071,16 +3216,22 @@
         <v>-100</v>
       </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,43 +3325,49 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>0</v>
+      <c r="D35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
       </c>
       <c r="G35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-100</v>
-      </c>
       <c r="M35" s="3">
         <v>-100</v>
       </c>
       <c r="N35" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O35" s="3">
         <v>-100</v>
@@ -3219,17 +3376,17 @@
         <v>-200</v>
       </c>
       <c r="Q35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-100</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
@@ -3237,7 +3394,7 @@
         <v>-100</v>
       </c>
       <c r="W35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3">
         <v>-100</v>
@@ -3246,13 +3403,13 @@
         <v>-100</v>
       </c>
       <c r="Z35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="3">
         <v>0</v>
@@ -3261,116 +3418,128 @@
         <v>-100</v>
       </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,8 +3610,10 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3532,10 +3705,16 @@
         <v>0</v>
       </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3548,26 +3727,26 @@
       <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>600</v>
-      </c>
-      <c r="L42" s="3">
-        <v>100</v>
-      </c>
-      <c r="M42" s="3">
-        <v>200</v>
       </c>
       <c r="N42" s="3">
         <v>100</v>
@@ -3576,13 +3755,13 @@
         <v>200</v>
       </c>
       <c r="P42" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="3">
         <v>200</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3629,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3909,14 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +4010,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3863,11 +4060,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
@@ -3881,11 +4078,11 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3914,8 +4111,14 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3938,16 +4141,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>600</v>
-      </c>
-      <c r="L46" s="3">
-        <v>100</v>
-      </c>
-      <c r="M46" s="3">
-        <v>200</v>
       </c>
       <c r="N46" s="3">
         <v>100</v>
@@ -3956,13 +4159,13 @@
         <v>200</v>
       </c>
       <c r="P46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S46" s="3">
         <v>0</v>
@@ -4007,10 +4210,16 @@
         <v>0</v>
       </c>
       <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,8 +4313,14 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4164,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="V48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X48" s="3">
         <v>100</v>
@@ -4181,11 +4396,11 @@
       <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
+      <c r="AB48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>100</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>4</v>
@@ -4199,8 +4414,14 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4579,8 +4818,14 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,8 +4919,14 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4698,19 +4949,19 @@
         <v>0</v>
       </c>
       <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3">
         <v>300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>100</v>
-      </c>
-      <c r="M54" s="3">
-        <v>200</v>
-      </c>
-      <c r="N54" s="3">
-        <v>200</v>
       </c>
       <c r="O54" s="3">
         <v>200</v>
@@ -4719,10 +4970,10 @@
         <v>200</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S54" s="3">
         <v>0</v>
@@ -4734,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="V54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X54" s="3">
         <v>100</v>
@@ -4752,10 +5003,10 @@
         <v>100</v>
       </c>
       <c r="AB54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD54" s="3">
         <v>0</v>
@@ -4767,10 +5018,16 @@
         <v>0</v>
       </c>
       <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,13 +5098,15 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>1400</v>
@@ -4857,43 +5118,43 @@
         <v>1400</v>
       </c>
       <c r="H57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>300</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
@@ -4914,10 +5175,10 @@
         <v>300</v>
       </c>
       <c r="AA57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC57" s="3">
         <v>200</v>
@@ -4934,8 +5195,14 @@
       <c r="AG57" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4949,26 +5216,26 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4979,17 +5246,17 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
@@ -5029,31 +5296,37 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5073,41 +5346,41 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5124,58 +5397,64 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
-        <v>1400</v>
-      </c>
       <c r="F60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G60" s="3">
         <v>1400</v>
       </c>
       <c r="H60" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I60" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J60" s="3">
         <v>1300</v>
       </c>
       <c r="K60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>300</v>
-      </c>
-      <c r="S60" s="3">
-        <v>300</v>
       </c>
       <c r="T60" s="3">
         <v>300</v>
@@ -5184,16 +5463,16 @@
         <v>300</v>
       </c>
       <c r="V60" s="3">
+        <v>300</v>
+      </c>
+      <c r="W60" s="3">
+        <v>300</v>
+      </c>
+      <c r="X60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>400</v>
-      </c>
-      <c r="X60" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>300</v>
       </c>
       <c r="Z60" s="3">
         <v>300</v>
@@ -5202,10 +5481,10 @@
         <v>300</v>
       </c>
       <c r="AB60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD60" s="3">
         <v>200</v>
@@ -5219,8 +5498,14 @@
       <c r="AG60" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5314,31 +5599,37 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,61 +6003,67 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
-        <v>1400</v>
-      </c>
       <c r="F66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G66" s="3">
         <v>1400</v>
       </c>
       <c r="H66" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I66" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J66" s="3">
         <v>1300</v>
       </c>
       <c r="K66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>300</v>
-      </c>
-      <c r="S66" s="3">
-        <v>300</v>
-      </c>
-      <c r="T66" s="3">
-        <v>400</v>
       </c>
       <c r="U66" s="3">
         <v>300</v>
@@ -5757,25 +6072,25 @@
         <v>400</v>
       </c>
       <c r="W66" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X66" s="3">
         <v>400</v>
       </c>
       <c r="Y66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA66" s="3">
         <v>300</v>
       </c>
       <c r="AB66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD66" s="3">
         <v>200</v>
@@ -5789,8 +6104,14 @@
       <c r="AG66" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI66" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,16 +6545,22 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-14200</v>
+        <v>-18600</v>
       </c>
       <c r="E72" s="3">
-        <v>-14200</v>
+        <v>-14900</v>
       </c>
       <c r="F72" s="3">
         <v>-14200</v>
@@ -6222,85 +6569,91 @@
         <v>-14200</v>
       </c>
       <c r="H72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="J72" s="3">
         <v>-14100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-13900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-13700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-13400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-13300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-13200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-13100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-13000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-12700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-12300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-11800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-11800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-11700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-11700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-11600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,16 +6949,22 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="E76" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="F76" s="3">
         <v>-1400</v>
@@ -6602,40 +6973,40 @@
         <v>-1400</v>
       </c>
       <c r="H76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J76" s="3">
         <v>-1300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-800</v>
       </c>
       <c r="M76" s="3">
         <v>-700</v>
       </c>
       <c r="N76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P76" s="3">
         <v>-600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-500</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S76" s="3">
-        <v>-300</v>
       </c>
       <c r="T76" s="3">
         <v>-300</v>
@@ -6656,10 +7027,10 @@
         <v>-300</v>
       </c>
       <c r="Z76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AA76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AB76" s="3">
         <v>-200</v>
@@ -6679,8 +7050,14 @@
       <c r="AG76" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI76" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,143 +7151,155 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>0</v>
+      <c r="D81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
       </c>
       <c r="G81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-100</v>
-      </c>
       <c r="M81" s="3">
         <v>-100</v>
       </c>
       <c r="N81" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O81" s="3">
         <v>-100</v>
@@ -6919,17 +7308,17 @@
         <v>-200</v>
       </c>
       <c r="Q81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-100</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
@@ -6937,7 +7326,7 @@
         <v>-100</v>
       </c>
       <c r="W81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X81" s="3">
         <v>-100</v>
@@ -6946,13 +7335,13 @@
         <v>-100</v>
       </c>
       <c r="Z81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="3">
         <v>0</v>
@@ -6961,16 +7350,22 @@
         <v>-100</v>
       </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7081,26 +7478,32 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,8 +8001,14 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7669,8 +8102,14 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +8143,10 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7799,8 +8240,14 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,13 +8442,19 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8016,43 +8475,43 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8084,8 +8543,14 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8984,14 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8526,14 +9017,14 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -8541,14 +9032,14 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8562,14 +9053,14 @@
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8594,8 +9085,14 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,8 +9186,14 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8782,6 +9285,12 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRWE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>CRWE</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,11 +866,11 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
@@ -900,8 +904,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,16 +1358,19 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -1361,8 +1381,8 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1370,11 +1390,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1392,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
@@ -1409,20 +1429,20 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1442,13 +1462,16 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1513,8 +1536,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
@@ -1522,11 +1545,11 @@
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>4</v>
@@ -1534,8 +1557,8 @@
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,20 +1603,21 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="E17" s="3">
+        <v>300</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
@@ -1598,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
@@ -1628,25 +1655,25 @@
         <v>100</v>
       </c>
       <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
       <c r="X17" s="3">
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3">
         <v>100</v>
@@ -1655,31 +1682,34 @@
         <v>100</v>
       </c>
       <c r="AB17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
       <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
         <v>100</v>
       </c>
-      <c r="AE17" s="3">
-        <v>0</v>
-      </c>
       <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
         <v>100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>300</v>
       </c>
-      <c r="AH17" s="3">
-        <v>0</v>
-      </c>
       <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1687,11 +1717,11 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
@@ -1699,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
@@ -1729,25 +1759,25 @@
         <v>-100</v>
       </c>
       <c r="S18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3">
         <v>-100</v>
@@ -1756,31 +1786,34 @@
         <v>-100</v>
       </c>
       <c r="AB18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC18" s="3">
         <v>0</v>
       </c>
       <c r="AD18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AH18" s="3">
-        <v>0</v>
-      </c>
       <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1825,7 +1859,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1843,17 +1877,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1879,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1917,8 +1951,11 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1926,11 +1963,11 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
@@ -1938,20 +1975,20 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-100</v>
       </c>
       <c r="K21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
-        <v>-100</v>
-      </c>
       <c r="N21" s="3">
         <v>-100</v>
       </c>
@@ -1959,23 +1996,23 @@
         <v>-100</v>
       </c>
       <c r="P21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
-        <v>-100</v>
-      </c>
       <c r="R21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
         <v>0</v>
       </c>
@@ -1986,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="Y21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
         <v>-100</v>
       </c>
       <c r="AA21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB21" s="3">
         <v>0</v>
@@ -2000,8 +2037,8 @@
       <c r="AC21" s="3">
         <v>0</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
+      <c r="AD21" s="3">
+        <v>0</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>4</v>
@@ -2009,17 +2046,20 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-300</v>
       </c>
-      <c r="AH21" s="3">
-        <v>0</v>
-      </c>
       <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2062,11 +2102,11 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2119,20 +2159,23 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-600</v>
       </c>
       <c r="E23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
@@ -2140,20 +2183,20 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
-        <v>-100</v>
-      </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
@@ -2161,31 +2204,31 @@
         <v>-100</v>
       </c>
       <c r="P23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="Q23" s="3">
-        <v>-100</v>
-      </c>
       <c r="R23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
         <v>-100</v>
@@ -2197,31 +2240,34 @@
         <v>-100</v>
       </c>
       <c r="AB23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC23" s="3">
         <v>0</v>
       </c>
       <c r="AD23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,20 +2471,23 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
         <v>0</v>
       </c>
@@ -2443,20 +2495,20 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
       </c>
       <c r="K26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
-        <v>-100</v>
-      </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
@@ -2464,31 +2516,31 @@
         <v>-100</v>
       </c>
       <c r="P26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
-        <v>-100</v>
-      </c>
       <c r="R26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
         <v>-100</v>
@@ -2500,43 +2552,46 @@
         <v>-100</v>
       </c>
       <c r="AB26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC26" s="3">
         <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-600</v>
       </c>
       <c r="E27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
@@ -2544,20 +2599,20 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
       </c>
       <c r="K27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
-        <v>-100</v>
-      </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
@@ -2565,31 +2620,31 @@
         <v>-100</v>
       </c>
       <c r="P27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
-        <v>-100</v>
-      </c>
       <c r="R27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>-100</v>
@@ -2601,31 +2656,34 @@
         <v>-100</v>
       </c>
       <c r="AB27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC27" s="3">
         <v>0</v>
       </c>
       <c r="AD27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3037,7 +3107,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -3055,16 +3125,16 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -3091,11 +3161,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3129,20 +3199,23 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-600</v>
       </c>
       <c r="E33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
         <v>0</v>
       </c>
@@ -3150,20 +3223,20 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>-100</v>
       </c>
       <c r="K33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
-        <v>-100</v>
-      </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
@@ -3171,31 +3244,31 @@
         <v>-100</v>
       </c>
       <c r="P33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
-        <v>-100</v>
-      </c>
       <c r="R33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
         <v>-100</v>
@@ -3207,31 +3280,34 @@
         <v>-100</v>
       </c>
       <c r="AB33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC33" s="3">
         <v>0</v>
       </c>
       <c r="AD33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,20 +3407,23 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-600</v>
       </c>
       <c r="E35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
         <v>0</v>
       </c>
@@ -3352,20 +3431,20 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>-100</v>
       </c>
       <c r="K35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
-        <v>-100</v>
-      </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
@@ -3373,31 +3452,31 @@
         <v>-100</v>
       </c>
       <c r="P35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
-        <v>-100</v>
-      </c>
       <c r="R35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
         <v>-100</v>
@@ -3409,137 +3488,143 @@
         <v>-100</v>
       </c>
       <c r="AB35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC35" s="3">
         <v>0</v>
       </c>
       <c r="AD35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,8 +3698,9 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3711,15 +3798,18 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>4</v>
@@ -3733,8 +3823,8 @@
       <c r="H42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3743,28 +3833,28 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>200</v>
       </c>
       <c r="R42" s="3">
         <v>200</v>
       </c>
       <c r="S42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3915,8 +4008,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4016,8 +4112,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4066,8 +4165,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
@@ -4084,8 +4183,8 @@
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -4117,8 +4216,11 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4147,28 +4249,28 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>200</v>
       </c>
       <c r="R46" s="3">
         <v>200</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -4216,10 +4318,13 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4385,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="X48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
         <v>100</v>
@@ -4402,8 +4510,8 @@
       <c r="AC48" s="3">
         <v>100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
+      <c r="AD48" s="3">
+        <v>100</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,8 +5048,11 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4955,16 +5081,16 @@
         <v>0</v>
       </c>
       <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>100</v>
-      </c>
-      <c r="O54" s="3">
-        <v>200</v>
       </c>
       <c r="P54" s="3">
         <v>200</v>
@@ -4976,7 +5102,7 @@
         <v>200</v>
       </c>
       <c r="S54" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T54" s="3">
         <v>0</v>
@@ -4991,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="X54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="3">
         <v>100</v>
@@ -5009,7 +5135,7 @@
         <v>100</v>
       </c>
       <c r="AD54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE54" s="3">
         <v>0</v>
@@ -5024,10 +5150,13 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,8 +5230,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5109,7 +5240,7 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>1400</v>
@@ -5124,40 +5255,40 @@
         <v>1400</v>
       </c>
       <c r="J57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>300</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
@@ -5181,7 +5312,7 @@
         <v>300</v>
       </c>
       <c r="AC57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD57" s="3">
         <v>200</v>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3">
         <v>200</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5222,7 +5356,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -5231,14 +5365,14 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5252,13 +5386,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
       </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5302,16 +5436,19 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
@@ -5328,8 +5465,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5352,14 +5489,14 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -5368,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
@@ -5376,14 +5513,14 @@
       <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
+      <c r="AA59" s="3">
+        <v>100</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5403,8 +5540,11 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5412,13 +5552,13 @@
         <v>300</v>
       </c>
       <c r="E60" s="3">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="F60" s="3">
         <v>1500</v>
       </c>
       <c r="G60" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H60" s="3">
         <v>1400</v>
@@ -5427,37 +5567,37 @@
         <v>1400</v>
       </c>
       <c r="J60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1300</v>
       </c>
       <c r="M60" s="3">
         <v>1300</v>
       </c>
       <c r="N60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
-      </c>
-      <c r="R60" s="3">
-        <v>500</v>
       </c>
       <c r="S60" s="3">
         <v>500</v>
       </c>
       <c r="T60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="U60" s="3">
         <v>300</v>
@@ -5469,13 +5609,13 @@
         <v>300</v>
       </c>
       <c r="X60" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>300</v>
@@ -5487,7 +5627,7 @@
         <v>300</v>
       </c>
       <c r="AD60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE60" s="3">
         <v>200</v>
@@ -5504,8 +5644,11 @@
       <c r="AI60" s="3">
         <v>200</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5605,34 +5748,37 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,22 +6164,25 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E66" s="3">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="F66" s="3">
         <v>1500</v>
       </c>
       <c r="G66" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="H66" s="3">
         <v>1400</v>
@@ -6033,49 +6191,49 @@
         <v>1400</v>
       </c>
       <c r="J66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1300</v>
       </c>
       <c r="M66" s="3">
         <v>1300</v>
       </c>
       <c r="N66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>600</v>
       </c>
       <c r="R66" s="3">
         <v>600</v>
       </c>
       <c r="S66" s="3">
+        <v>600</v>
+      </c>
+      <c r="T66" s="3">
         <v>500</v>
-      </c>
-      <c r="T66" s="3">
-        <v>300</v>
       </c>
       <c r="U66" s="3">
         <v>300</v>
       </c>
       <c r="V66" s="3">
+        <v>300</v>
+      </c>
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>300</v>
-      </c>
-      <c r="X66" s="3">
-        <v>400</v>
       </c>
       <c r="Y66" s="3">
         <v>400</v>
@@ -6084,7 +6242,7 @@
         <v>400</v>
       </c>
       <c r="AA66" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AB66" s="3">
         <v>300</v>
@@ -6093,7 +6251,7 @@
         <v>300</v>
       </c>
       <c r="AD66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE66" s="3">
         <v>200</v>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3">
         <v>200</v>
       </c>
+      <c r="AJ66" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,19 +6722,22 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-18600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-14200</v>
       </c>
       <c r="G72" s="3">
         <v>-14200</v>
@@ -6575,85 +6749,88 @@
         <v>-14200</v>
       </c>
       <c r="J72" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-14100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-13000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-12300</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-11800</v>
       </c>
       <c r="V72" s="3">
         <v>-11800</v>
       </c>
       <c r="W72" s="3">
-        <v>-11700</v>
+        <v>-11800</v>
       </c>
       <c r="X72" s="3">
         <v>-11700</v>
       </c>
       <c r="Y72" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11400</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>-11300</v>
       </c>
       <c r="AC72" s="3">
         <v>-11300</v>
       </c>
       <c r="AD72" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="AE72" s="3">
         <v>-11200</v>
       </c>
       <c r="AF72" s="3">
-        <v>-11100</v>
+        <v>-11200</v>
       </c>
       <c r="AG72" s="3">
         <v>-11100</v>
       </c>
       <c r="AH72" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="AI72" s="3">
         <v>-10800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,8 +7138,11 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6964,10 +7150,10 @@
         <v>-300</v>
       </c>
       <c r="E76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-1400</v>
       </c>
       <c r="G76" s="3">
         <v>-1400</v>
@@ -6979,37 +7165,37 @@
         <v>-1400</v>
       </c>
       <c r="J76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K76" s="3">
         <v>-1300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-600</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-400</v>
       </c>
       <c r="R76" s="3">
         <v>-400</v>
       </c>
       <c r="S76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T76" s="3">
         <v>-500</v>
-      </c>
-      <c r="T76" s="3">
-        <v>-300</v>
       </c>
       <c r="U76" s="3">
         <v>-300</v>
@@ -7033,7 +7219,7 @@
         <v>-300</v>
       </c>
       <c r="AB76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC76" s="3">
         <v>-200</v>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3">
         <v>-200</v>
       </c>
+      <c r="AJ76" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,126 +7346,132 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-600</v>
       </c>
       <c r="E81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
         <v>0</v>
       </c>
@@ -7284,20 +7479,20 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
         <v>-100</v>
       </c>
       <c r="K81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
-        <v>-100</v>
-      </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
@@ -7305,31 +7500,31 @@
         <v>-100</v>
       </c>
       <c r="P81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
-        <v>-100</v>
-      </c>
       <c r="R81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="3">
         <v>-100</v>
@@ -7341,31 +7536,34 @@
         <v>-100</v>
       </c>
       <c r="AB81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC81" s="3">
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7484,8 +7683,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>4</v>
@@ -7493,8 +7692,8 @@
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8221,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,13 +8675,16 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -8481,22 +8711,22 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
@@ -8504,17 +8734,17 @@
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9023,11 +9269,11 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -9038,11 +9284,11 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -9059,11 +9305,11 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -9091,8 +9337,11 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9192,8 +9441,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9291,6 +9543,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>
